--- a/AAII_Financials/Yearly/PRMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>PRMY</t>
   </si>
@@ -972,7 +972,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12300</v>
+        <v>12000</v>
       </c>
       <c r="E17" s="3">
         <v>11300</v>
@@ -1005,7 +1005,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>15700</v>
+        <v>16000</v>
       </c>
       <c r="E18" s="3">
         <v>14900</v>
@@ -1052,8 +1052,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
@@ -1448,8 +1448,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>-300</v>
@@ -1747,8 +1747,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>3700</v>
       </c>
       <c r="E44" s="3">
         <v>1000</v>
@@ -1780,8 +1780,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>2000</v>
       </c>
       <c r="E45" s="3">
         <v>2000</v>
@@ -1814,7 +1814,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>66700</v>
+        <v>72300</v>
       </c>
       <c r="E46" s="3">
         <v>98100</v>
@@ -1847,10 +1847,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>13900</v>
+        <v>14200</v>
       </c>
       <c r="E47" s="3">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="F47" s="3">
         <v>9600</v>
@@ -1879,8 +1879,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>2000</v>
       </c>
       <c r="E48" s="3">
         <v>2500</v>
@@ -2012,10 +2012,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10500</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="F52" s="3">
         <v>2300</v>
@@ -2174,10 +2174,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2240,10 +2240,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>605300</v>
+        <v>608600</v>
       </c>
       <c r="E60" s="3">
-        <v>607700</v>
+        <v>607300</v>
       </c>
       <c r="F60" s="3">
         <v>603700</v>
@@ -2273,10 +2273,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E61" s="3">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="F61" s="3">
         <v>2000</v>
@@ -2305,8 +2305,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>4400</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>5</v>
@@ -2901,8 +2901,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -3099,8 +3099,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>10800</v>
       </c>
       <c r="E89" s="3">
         <v>12800</v>
@@ -3147,8 +3147,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3246,8 +3246,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>-42100</v>
       </c>
       <c r="E94" s="3">
         <v>-13000</v>
@@ -3426,8 +3426,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>2800</v>
       </c>
       <c r="E100" s="3">
         <v>4000</v>
@@ -3493,7 +3493,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-28400</v>
       </c>
       <c r="E102" s="3">
         <v>3800</v>
